--- a/data/GPS/Metricas_GPS (2).xlsx
+++ b/data/GPS/Metricas_GPS (2).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30405"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E1D0ED-B08D-4892-BF23-156117DBAC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{39E1D0ED-B08D-4892-BF23-156117DBAC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25F9BDDF-178B-4034-A570-963C3B75EC86}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>eJy9lltv0zAUx7+KlSeQqjTNIEQIIRWqvbCVbmgb46LJtd3Gqy9RbK9bq353bLeMJLRlDVqeknNyfM7vf3zLMsBQExW8BctAS/9wDvsSxFGcRGmUBB0Q3EHmXMzF6mBlPZNC8qeGu/j8TqPJ1BX6vtwYNxS7KG4MhguapHM3FEm2CbJvm4iFmFP3LYc6c7YvaW39kJOyLSD39jFBGXQOI6h2DkdcTsgiq9V+p+pm6uknkCliHQXBBvkcWmpfAk4xmayH9ZKkF1sfEYZbj8f8WcLKpQpJjspkdniZg1NR5hyYAiIqRR3vGJ5dlvX6+FLWnMEHUpQzDSUfF2Sf5G/n8cegCku1q70378hGoU3UrsyYmtutzRwXRmXksU3/3VtM1Z7ezniltVRpKBCFwBazq7HG/Cm7SivMujDPgbwQJHzVEPw96KVgxrtZHf4kMVlb8ElDeEsfv+7EYKuAz/zitC0BbxoKcP2P0066XcGZhPftTQESeo+Cyjnww0TRGIIveUGFVuDFuz+z8PKvdSQ+9NsQARFyOuIGOvqIMLI+JC1Qjb93/rWVTYxJY/4BUXCfhIuhuj7s7OTrhddgDsLfQ3fcTV3VVWUNfRSCU3hPOaxToxHBB1KvL75G1FQcQj0gO7HzydFRK81WOf5Hs91+rFy0lx66TjyIr4fPfrXSWxUyiZ+4skf+HwGcSIiDlUuDGCVCr0sJw5h3Pu4DMgdXspiNpZwFq19ONxAM</t>
   </si>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jorge_vicaria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alejandro_Garcia_Gumiel </t>
   </si>
   <si>
     <t xml:space="preserve">Gonzalo_Echavarria </t>
@@ -443,7 +440,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="22.21875" customWidth="1"/>
@@ -789,40 +786,40 @@
         <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2">
-        <v>5.5060000000000002</v>
+        <v>6.5119999999999996</v>
       </c>
       <c r="F8" s="2">
-        <v>0.23699999999999999</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="G8" s="2">
-        <v>1.7999999999999999E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="K8" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="L8" s="2">
-        <v>4.37</v>
+        <v>5.1369999999999996</v>
       </c>
       <c r="M8" s="2">
-        <v>-5.3780000000000001</v>
+        <v>-5.7080000000000002</v>
       </c>
       <c r="N8" s="2">
-        <v>27.544</v>
+        <v>28.094000000000001</v>
       </c>
       <c r="O8" s="2">
-        <v>1314.2</v>
+        <v>1137.9000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -833,43 +830,43 @@
         <v>91.055000000000007</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2">
-        <v>6.5119999999999996</v>
+        <v>5.593</v>
       </c>
       <c r="F9" s="2">
-        <v>0.34799999999999998</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>2.1000000000000001E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K9" s="2">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L9" s="2">
-        <v>5.1369999999999996</v>
+        <v>5.0430000000000001</v>
       </c>
       <c r="M9" s="2">
-        <v>-5.7080000000000002</v>
+        <v>-5.6319999999999997</v>
       </c>
       <c r="N9" s="2">
-        <v>28.094000000000001</v>
+        <v>27.391999999999999</v>
       </c>
       <c r="O9" s="2">
-        <v>1137.9000000000001</v>
+        <v>1202.9000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -883,40 +880,40 @@
         <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2">
-        <v>5.593</v>
+        <v>7.3010000000000002</v>
       </c>
       <c r="F10" s="2">
-        <v>0.19900000000000001</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="G10" s="2">
-        <v>1.2999999999999999E-2</v>
+        <v>0.05</v>
       </c>
       <c r="H10" s="2">
-        <v>0</v>
+        <v>2E-3</v>
       </c>
       <c r="I10" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J10" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K10" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="L10" s="2">
-        <v>5.0430000000000001</v>
+        <v>4.851</v>
       </c>
       <c r="M10" s="2">
-        <v>-5.6319999999999997</v>
+        <v>-6.3929999999999998</v>
       </c>
       <c r="N10" s="2">
-        <v>27.391999999999999</v>
+        <v>29.416</v>
       </c>
       <c r="O10" s="2">
-        <v>1202.9000000000001</v>
+        <v>1708.2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -930,40 +927,40 @@
         <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2">
-        <v>7.3010000000000002</v>
+        <v>6.1849999999999996</v>
       </c>
       <c r="F11" s="2">
-        <v>0.59299999999999997</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="G11" s="2">
-        <v>0.05</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="H11" s="2">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="K11" s="2">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="L11" s="2">
-        <v>4.851</v>
+        <v>5.0369999999999999</v>
       </c>
       <c r="M11" s="2">
-        <v>-6.3929999999999998</v>
+        <v>-5.3710000000000004</v>
       </c>
       <c r="N11" s="2">
-        <v>29.416</v>
+        <v>26.492000000000001</v>
       </c>
       <c r="O11" s="2">
-        <v>1708.2</v>
+        <v>1613.2</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -980,37 +977,37 @@
         <v>19</v>
       </c>
       <c r="E12" s="2">
-        <v>6.1849999999999996</v>
+        <v>2.9460000000000002</v>
       </c>
       <c r="F12" s="2">
-        <v>0.27100000000000002</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="G12" s="2">
-        <v>8.0000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="K12" s="2">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="L12" s="2">
-        <v>5.0369999999999999</v>
+        <v>3.9510000000000001</v>
       </c>
       <c r="M12" s="2">
-        <v>-5.3710000000000004</v>
+        <v>-4.2619999999999996</v>
       </c>
       <c r="N12" s="2">
-        <v>26.492000000000001</v>
+        <v>23.417999999999999</v>
       </c>
       <c r="O12" s="2">
-        <v>1613.2</v>
+        <v>523.5</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1024,40 +1021,40 @@
         <v>34</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2">
-        <v>2.9460000000000002</v>
+        <v>5.6909999999999998</v>
       </c>
       <c r="F13" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="G13" s="2">
-        <v>0</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="H13" s="2">
-        <v>0</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13" s="2">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="K13" s="2">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="L13" s="2">
-        <v>3.9510000000000001</v>
+        <v>4.7610000000000001</v>
       </c>
       <c r="M13" s="2">
-        <v>-4.2619999999999996</v>
+        <v>-5.6420000000000003</v>
       </c>
       <c r="N13" s="2">
-        <v>23.417999999999999</v>
+        <v>31.161999999999999</v>
       </c>
       <c r="O13" s="2">
-        <v>523.5</v>
+        <v>1382.5</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1071,40 +1068,40 @@
         <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2">
-        <v>5.6909999999999998</v>
+        <v>5.125</v>
       </c>
       <c r="F14" s="2">
-        <v>0.36699999999999999</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="G14" s="2">
-        <v>4.3999999999999997E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="H14" s="2">
-        <v>1.2999999999999999E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="I14" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="K14" s="2">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="L14" s="2">
-        <v>4.7610000000000001</v>
+        <v>4.2060000000000004</v>
       </c>
       <c r="M14" s="2">
-        <v>-5.6420000000000003</v>
+        <v>-4.8780000000000001</v>
       </c>
       <c r="N14" s="2">
-        <v>31.161999999999999</v>
+        <v>29.326000000000001</v>
       </c>
       <c r="O14" s="2">
-        <v>1382.5</v>
+        <v>1070.9000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1115,89 +1112,42 @@
         <v>91.055000000000007</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E15" s="2">
-        <v>5.125</v>
+        <v>4.9359999999999999</v>
       </c>
       <c r="F15" s="2">
-        <v>0.27800000000000002</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="G15" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="H15" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="K15" s="2">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L15" s="2">
-        <v>4.2060000000000004</v>
+        <v>5.0579999999999998</v>
       </c>
       <c r="M15" s="2">
-        <v>-4.8780000000000001</v>
+        <v>-5.7489999999999997</v>
       </c>
       <c r="N15" s="2">
-        <v>29.326000000000001</v>
+        <v>26.995999999999999</v>
       </c>
       <c r="O15" s="2">
-        <v>1070.9000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>46240</v>
-      </c>
-      <c r="B16" s="2">
-        <v>91.055000000000007</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="2">
-        <v>4.9359999999999999</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0.33400000000000002</v>
-      </c>
-      <c r="G16" s="2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>2</v>
-      </c>
-      <c r="J16" s="2">
-        <v>52</v>
-      </c>
-      <c r="K16" s="2">
-        <v>39</v>
-      </c>
-      <c r="L16" s="2">
-        <v>5.0579999999999998</v>
-      </c>
-      <c r="M16" s="2">
-        <v>-5.7489999999999997</v>
-      </c>
-      <c r="N16" s="2">
-        <v>26.995999999999999</v>
-      </c>
-      <c r="O16" s="2">
         <v>1267.5</v>
       </c>
     </row>
